--- a/data/trans_camb/IP19C02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Edad-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,68</t>
+          <t>0,0; 79,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,83; 63,86</t>
+          <t>7,92; 66,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,46; 74,76</t>
+          <t>11,18; 74,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,11</t>
+          <t>0,0; 65,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,83; 57,8</t>
+          <t>15,21; 60,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 4,54</t>
+          <t>-4,25; 4,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 16,0</t>
+          <t>2,27; 15,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 25,76</t>
+          <t>8,92; 26,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 5,91</t>
+          <t>-3,56; 5,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 14,08</t>
+          <t>1,68; 13,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,31; 43,9</t>
+          <t>23,61; 43,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,58</t>
+          <t>-3,05; 3,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,65; 12,92</t>
+          <t>3,38; 12,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,15; 33,1</t>
+          <t>18,58; 33,12</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-92,04; 302,73</t>
+          <t>-82,07; 371,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 1095,37</t>
+          <t>22,42; 1185,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99,66; 1619,24</t>
+          <t>129,91; 1834,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-80,67; 640,56</t>
+          <t>-80,61; 673,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 1157,8</t>
+          <t>-4,76; 1099,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>342,82; 4942,08</t>
+          <t>367,94; 4513,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,04; 195,94</t>
+          <t>-63,89; 258,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,81; 687,77</t>
+          <t>48,15; 706,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>353,28; 1840,27</t>
+          <t>299,98; 1905,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 1,08</t>
+          <t>-9,0; 0,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 17,36</t>
+          <t>3,91; 17,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,0; 31,67</t>
+          <t>14,64; 31,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 3,3</t>
+          <t>-8,13; 2,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 16,46</t>
+          <t>2,42; 16,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 21,01</t>
+          <t>6,37; 20,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,77</t>
+          <t>-6,92; 0,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 15,12</t>
+          <t>5,41; 14,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,34; 23,11</t>
+          <t>12,73; 23,15</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-83,61; 41,26</t>
+          <t>-82,19; 57,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,85; 394,1</t>
+          <t>30,13; 380,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>132,66; 696,58</t>
+          <t>116,02; 709,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-69,32; 86,84</t>
+          <t>-69,56; 59,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,12; 323,1</t>
+          <t>18,44; 313,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,74; 420,06</t>
+          <t>46,56; 402,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,34; 18,15</t>
+          <t>-68,31; 10,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>47,75; 266,96</t>
+          <t>51,13; 267,97</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>119,27; 408,84</t>
+          <t>116,79; 413,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 4,66</t>
+          <t>-6,35; 3,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,04; 20,78</t>
+          <t>7,51; 20,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,8; 29,5</t>
+          <t>16,61; 30,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 6,21</t>
+          <t>-3,95; 5,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,35; 26,81</t>
+          <t>12,51; 26,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,98; 36,84</t>
+          <t>21,45; 36,38</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,89</t>
+          <t>-3,42; 3,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,7; 21,73</t>
+          <t>11,69; 21,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,62; 31,33</t>
+          <t>21,25; 31,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,26; 69,72</t>
+          <t>-54,57; 57,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>57,16; 320,59</t>
+          <t>52,82; 291,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>120,6; 433,79</t>
+          <t>127,67; 453,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,41; 117,03</t>
+          <t>-40,57; 107,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>123,66; 539,77</t>
+          <t>127,42; 499,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>211,69; 712,47</t>
+          <t>205,02; 699,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 58,56</t>
+          <t>-34,28; 57,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>109,56; 319,39</t>
+          <t>113,35; 325,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>203,08; 468,29</t>
+          <t>204,67; 469,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,55</t>
+          <t>-4,69; 1,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,55; 15,62</t>
+          <t>7,84; 15,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,6; 26,88</t>
+          <t>17,83; 27,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,72</t>
+          <t>-3,35; 2,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,86; 16,75</t>
+          <t>8,77; 17,06</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,39; 29,93</t>
+          <t>20,17; 30,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,21</t>
+          <t>-3,19; 1,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,25; 14,93</t>
+          <t>9,57; 15,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,52; 27,09</t>
+          <t>20,2; 27,1</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,04; 28,52</t>
+          <t>-50,66; 29,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>81,22; 271,1</t>
+          <t>85,75; 277,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195,61; 482,5</t>
+          <t>195,16; 490,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 51,73</t>
+          <t>-40,42; 52,99</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>109,15; 321,82</t>
+          <t>105,21; 330,28</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>238,63; 593,22</t>
+          <t>233,43; 562,85</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-37,85; 20,54</t>
+          <t>-40,26; 18,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>112,14; 258,28</t>
+          <t>118,61; 253,58</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>250,88; 465,36</t>
+          <t>242,06; 445,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Edad-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 79,1</t>
+          <t>0,0; 80,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 66,92</t>
+          <t>9,74; 71,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,12 +702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 74,76</t>
+          <t>11,43; 75,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,4</t>
+          <t>0,0; 66,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,21; 60,48</t>
+          <t>14,4; 56,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,65</t>
+          <t>-4,86; 4,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 15,45</t>
+          <t>1,77; 15,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,92; 26,09</t>
+          <t>9,12; 26,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 5,7</t>
+          <t>-4,29; 5,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 13,98</t>
+          <t>1,77; 14,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,61; 43,63</t>
+          <t>22,56; 43,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 3,79</t>
+          <t>-2,68; 3,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 12,81</t>
+          <t>3,38; 12,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,58; 33,12</t>
+          <t>19,37; 33,03</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,07; 371,53</t>
+          <t>-86,93; 356,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,42; 1185,14</t>
+          <t>4,06; 943,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129,91; 1834,64</t>
+          <t>128,64; 1885,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-80,61; 673,41</t>
+          <t>-87,78; 590,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 1099,88</t>
+          <t>8,95; 1474,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>367,94; 4513,34</t>
+          <t>363,99; 4358,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,89; 258,37</t>
+          <t>-62,45; 220,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,15; 706,33</t>
+          <t>57,85; 689,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>299,98; 1905,42</t>
+          <t>377,71; 1885,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 0,94</t>
+          <t>-9,07; 1,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 17,1</t>
+          <t>3,79; 17,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 31,49</t>
+          <t>13,93; 30,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 2,82</t>
+          <t>-7,81; 2,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 16,14</t>
+          <t>3,62; 16,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 20,72</t>
+          <t>6,33; 20,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 0,36</t>
+          <t>-7,05; 0,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,41; 14,93</t>
+          <t>4,83; 14,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,73; 23,15</t>
+          <t>12,42; 23,38</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,19; 57,4</t>
+          <t>-83,88; 47,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30,13; 380,65</t>
+          <t>28,48; 419,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>116,02; 709,62</t>
+          <t>119,34; 728,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-69,56; 59,89</t>
+          <t>-69,76; 54,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,44; 313,69</t>
+          <t>30,25; 326,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46,56; 402,43</t>
+          <t>52,35; 399,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,31; 10,2</t>
+          <t>-69,18; 9,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,13; 267,97</t>
+          <t>44,53; 263,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>116,79; 413,11</t>
+          <t>121,33; 414,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 3,98</t>
+          <t>-6,03; 3,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,51; 20,82</t>
+          <t>6,96; 21,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,61; 30,24</t>
+          <t>16,2; 30,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 5,55</t>
+          <t>-3,57; 5,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,51; 26,0</t>
+          <t>11,91; 26,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,45; 36,38</t>
+          <t>20,99; 36,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 3,86</t>
+          <t>-3,58; 3,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,69; 21,94</t>
+          <t>11,53; 21,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,25; 31,41</t>
+          <t>21,15; 31,62</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,57; 57,83</t>
+          <t>-52,37; 62,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,82; 291,76</t>
+          <t>54,09; 301,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>127,67; 453,55</t>
+          <t>127,38; 449,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,57; 107,49</t>
+          <t>-39,52; 114,47</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>127,42; 499,5</t>
+          <t>111,04; 516,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>205,02; 699,9</t>
+          <t>202,67; 709,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,28; 57,66</t>
+          <t>-35,73; 57,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>113,35; 325,51</t>
+          <t>116,88; 336,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>204,67; 469,5</t>
+          <t>202,89; 491,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 1,65</t>
+          <t>-4,59; 1,27</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,84; 15,89</t>
+          <t>7,72; 15,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,83; 27,53</t>
+          <t>17,62; 26,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,74</t>
+          <t>-3,47; 2,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,77; 17,06</t>
+          <t>9,09; 17,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,17; 30,08</t>
+          <t>20,09; 29,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 1,14</t>
+          <t>-3,03; 1,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,57; 15,22</t>
+          <t>9,73; 15,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,2; 27,1</t>
+          <t>20,52; 27,43</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 29,71</t>
+          <t>-52,23; 22,77</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>85,75; 277,32</t>
+          <t>79,23; 258,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195,16; 490,86</t>
+          <t>191,82; 456,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-40,42; 52,99</t>
+          <t>-41,29; 49,25</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>105,21; 330,28</t>
+          <t>109,37; 330,73</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>233,43; 562,85</t>
+          <t>235,84; 601,88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-40,26; 18,37</t>
+          <t>-37,67; 17,56</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>118,61; 253,58</t>
+          <t>115,9; 257,19</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>242,06; 445,98</t>
+          <t>253,06; 470,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP19C02-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>36,32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>19,02</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>31,87</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,71</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,81</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,39</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,81</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>34,03</t>
+          <t>33,71</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,74; 71,31</t>
+          <t>10,66; 75,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 76,68</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,66; 64,67</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 66,11</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,43; 75,06</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 66,77</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,4; 56,78</t>
+          <t>16,05; 57,51</t>
         </is>
       </c>
     </row>
@@ -730,22 +730,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,23</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32,85</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,36</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>17,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,23</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,87</t>
+          <t>18,34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25,62</t>
+          <t>25,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 4,22</t>
+          <t>-3,66; 5,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 15,74</t>
+          <t>1,44; 14,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,12; 26,44</t>
+          <t>23,02; 43,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 5,51</t>
+          <t>-4,67; 4,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 14,48</t>
+          <t>2,22; 16,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,56; 43,28</t>
+          <t>9,06; 27,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,6</t>
+          <t>-3,07; 3,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 12,73</t>
+          <t>3,65; 12,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,37; 33,03</t>
+          <t>18,76; 32,7</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20,98%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>233,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1059,29%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-3,87%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>239,78%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>494,01%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20,98%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>233,2%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1059,94%</t>
+          <t>526,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>776,93%</t>
+          <t>782,64%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-86,93; 356,55</t>
+          <t>-80,67; 640,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,06; 943,83</t>
+          <t>2,74; 1157,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128,64; 1885,32</t>
+          <t>335,83; 4846,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,78; 590,36</t>
+          <t>-92,04; 302,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,95; 1474,12</t>
+          <t>2,91; 1095,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>363,99; 4358,65</t>
+          <t>114,83; 1703,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,45; 220,27</t>
+          <t>-64,04; 195,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,85; 689,12</t>
+          <t>57,81; 687,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>377,71; 1885,76</t>
+          <t>357,83; 1822,41</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,42</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,82</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16,16</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-3,74</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>10,76</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22,9</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,42</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,82</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,56</t>
+          <t>25,18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17,59</t>
+          <t>20,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 1,03</t>
+          <t>-7,91; 3,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 17,03</t>
+          <t>2,72; 16,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,93; 30,17</t>
+          <t>8,14; 24,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 2,58</t>
+          <t>-9,31; 1,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,62; 16,34</t>
+          <t>3,82; 17,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 20,77</t>
+          <t>17,14; 33,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 0,28</t>
+          <t>-6,77; 0,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,83; 14,95</t>
+          <t>5,19; 15,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,42; 23,38</t>
+          <t>14,66; 26,11</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-29,44%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>119,19%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>196,19%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-51,1%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>147,14%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>313,12%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-29,44%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>119,19%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>164,67%</t>
+          <t>344,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>225,79%</t>
+          <t>258,84%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-83,88; 47,85</t>
+          <t>-69,32; 86,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,48; 419,53</t>
+          <t>18,12; 323,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>119,34; 728,18</t>
+          <t>68,33; 486,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-69,76; 54,06</t>
+          <t>-83,61; 41,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,25; 326,21</t>
+          <t>30,85; 394,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,35; 399,31</t>
+          <t>152,62; 743,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,18; 9,8</t>
+          <t>-69,34; 18,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44,53; 263,23</t>
+          <t>47,75; 266,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>121,33; 414,94</t>
+          <t>144,52; 460,94</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19,53</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31,76</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,93</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>13,78</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>22,83</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>19,53</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,19</t>
+          <t>24,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>26,24</t>
+          <t>28,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 3,97</t>
+          <t>-3,47; 6,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 21,17</t>
+          <t>12,35; 26,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,2; 30,15</t>
+          <t>23,73; 39,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 5,84</t>
+          <t>-6,18; 4,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,91; 26,22</t>
+          <t>7,04; 20,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,99; 36,53</t>
+          <t>17,01; 30,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 3,73</t>
+          <t>-3,7; 3,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,53; 21,46</t>
+          <t>11,7; 21,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,15; 31,62</t>
+          <t>22,64; 33,5</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>262,16%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>426,28%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-9,83%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>144,96%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>240,13%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>262,16%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>391,78%</t>
+          <t>253,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>310,57%</t>
+          <t>333,22%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,37; 62,06</t>
+          <t>-37,41; 117,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>54,09; 301,35</t>
+          <t>123,66; 539,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>127,38; 449,78</t>
+          <t>234,5; 758,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,52; 114,47</t>
+          <t>-52,26; 69,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>111,04; 516,52</t>
+          <t>57,16; 320,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>202,67; 709,13</t>
+          <t>131,93; 453,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 57,59</t>
+          <t>-35,08; 58,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>116,88; 336,13</t>
+          <t>109,56; 319,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>202,89; 491,41</t>
+          <t>225,26; 507,86</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,33</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12,87</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>27,04</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>11,63</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>22,37</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>12,87</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,81</t>
+          <t>24,02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>23,69</t>
+          <t>25,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 1,27</t>
+          <t>-3,09; 2,72</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,72; 15,71</t>
+          <t>8,86; 16,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,62; 26,54</t>
+          <t>22,45; 32,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,53</t>
+          <t>-4,53; 1,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,09; 17,39</t>
+          <t>7,55; 15,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,09; 29,84</t>
+          <t>19,22; 28,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,07</t>
+          <t>-3,07; 1,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9,73; 15,3</t>
+          <t>9,25; 14,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20,52; 27,43</t>
+          <t>22,4; 29,03</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-4,97%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>192,91%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>405,14%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-21,42%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>158,58%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>304,99%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-4,97%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>192,91%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>371,71%</t>
+          <t>327,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>338,43%</t>
+          <t>366,09%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 22,77</t>
+          <t>-39,01; 51,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>79,23; 258,15</t>
+          <t>109,15; 321,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>191,82; 456,57</t>
+          <t>257,44; 635,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,29; 49,25</t>
+          <t>-50,04; 28,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>109,37; 330,73</t>
+          <t>81,22; 271,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>235,84; 601,88</t>
+          <t>217,28; 526,78</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 17,56</t>
+          <t>-37,85; 20,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>115,9; 257,19</t>
+          <t>112,14; 258,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>253,06; 470,21</t>
+          <t>272,29; 503,43</t>
         </is>
       </c>
     </row>
